--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8940,0.0625,0.0331,0.0058</t>
-  </si>
-  <si>
-    <t>0.9311,0.0145,0.0270,0.0075</t>
-  </si>
-  <si>
-    <t>0.9615,0.0183,0.0139,0.0018</t>
-  </si>
-  <si>
-    <t>0.9765,0.0069,0.0064,0.0022</t>
-  </si>
-  <si>
-    <t>0.8626,0.0916,0.0043,0.0035</t>
-  </si>
-  <si>
-    <t>0.8484,0.0419,0.0052,0.0178</t>
-  </si>
-  <si>
-    <t>0.8557,0.0692,0.0246,0.0262</t>
-  </si>
-  <si>
-    <t>0.8624,0.0818,0.0064,0.0076</t>
-  </si>
-  <si>
-    <t>0.8558,0.1329,0.0149,0.0075</t>
-  </si>
-  <si>
-    <t>0.8687,0.0787,0.0139,0.0134</t>
-  </si>
-  <si>
-    <t>0.7322,0.2291,0.0163,0.0137</t>
-  </si>
-  <si>
-    <t>0.7379,0.2041,0.0200,0.0065</t>
-  </si>
-  <si>
-    <t>0.9296,0.0297,0.0340,0.0009</t>
-  </si>
-  <si>
-    <t>0.9945,0.0017,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9917,0.0015,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9005,0.0510,0.0318,0.0004</t>
-  </si>
-  <si>
-    <t>0.9362,0.0189,0.0505,0.0008</t>
-  </si>
-  <si>
-    <t>0.7613,0.3002,0.0052,0.0005</t>
-  </si>
-  <si>
-    <t>0.5170,0.6374,0.0061,0.0011</t>
-  </si>
-  <si>
-    <t>0.9247,0.0745,0.0084,0.0013</t>
-  </si>
-  <si>
-    <t>0.5721,0.5713,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.4063,0.7147,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0013,0.0165,0.0002</t>
-  </si>
-  <si>
-    <t>0.9714,0.0043,0.0281,0.0012</t>
-  </si>
-  <si>
-    <t>0.9761,0.0009,0.0555,0.0003</t>
-  </si>
-  <si>
-    <t>0.9836,0.0043,0.0095,0.0001</t>
-  </si>
-  <si>
-    <t>0.9755,0.0095,0.0106,0.0005</t>
-  </si>
-  <si>
-    <t>0.9160,0.0233,0.0645,0.0014</t>
-  </si>
-  <si>
-    <t>0.8937,0.0357,0.0908,0.0022</t>
-  </si>
-  <si>
-    <t>0.8564,0.2483,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9818,0.0094,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.1785,0.1327,0.8402,0.0026</t>
-  </si>
-  <si>
-    <t>0.9444,0.0478,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.8591,0.1265,0.0255,0.0046</t>
-  </si>
-  <si>
-    <t>0.9449,0.0264,0.0251,0.0019</t>
-  </si>
-  <si>
-    <t>0.6029,0.5069,0.0048,0.0011</t>
-  </si>
-  <si>
-    <t>0.9753,0.0314,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.3446,0.1687,0.6993,0.0038</t>
-  </si>
-  <si>
-    <t>0.8910,0.0248,0.1299,0.0033</t>
-  </si>
-  <si>
-    <t>0.9645,0.0059,0.0465,0.0026</t>
-  </si>
-  <si>
-    <t>0.9922,0.0021,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.9924,0.0006,0.0124,0.0002</t>
-  </si>
-  <si>
-    <t>0.7257,0.2757,0.0250,0.0036</t>
-  </si>
-  <si>
-    <t>0.9594,0.0051,0.0569,0.0011</t>
-  </si>
-  <si>
-    <t>0.9533,0.0184,0.0188,0.0040</t>
-  </si>
-  <si>
-    <t>0.5472,0.6277,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.8864,0.1809,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.2985,0.8190,0.0074,0.0008</t>
-  </si>
-  <si>
-    <t>0.8284,0.0346,0.1954,0.0026</t>
-  </si>
-  <si>
-    <t>0.7838,0.0728,0.1808,0.0016</t>
-  </si>
-  <si>
-    <t>0.9847,0.0023,0.0187,0.0003</t>
-  </si>
-  <si>
-    <t>0.9761,0.0023,0.0422,0.0004</t>
-  </si>
-  <si>
-    <t>0.5002,0.0266,0.5740,0.0012</t>
-  </si>
-  <si>
-    <t>0.9000,0.0166,0.1142,0.0004</t>
-  </si>
-  <si>
-    <t>0.8549,0.1654,0.0037,0.0013</t>
-  </si>
-  <si>
-    <t>0.8525,0.1200,0.0135,0.0056</t>
-  </si>
-  <si>
-    <t>0.8118,0.2002,0.0088,0.0047</t>
-  </si>
-  <si>
-    <t>0.1494,0.6005,0.6247,0.0109</t>
-  </si>
-  <si>
-    <t>0.9261,0.0313,0.0166,0.0096</t>
-  </si>
-  <si>
-    <t>0.8017,0.1467,0.0252,0.0176</t>
-  </si>
-  <si>
-    <t>0.9223,0.0688,0.0046,0.0023</t>
-  </si>
-  <si>
-    <t>0.0338,0.8165,0.7753,0.0007</t>
-  </si>
-  <si>
-    <t>0.8978,0.0056,0.3335,0.0002</t>
-  </si>
-  <si>
-    <t>0.4607,0.1861,0.4489,0.0062</t>
-  </si>
-  <si>
-    <t>0.0840,0.8043,0.4699,0.0020</t>
-  </si>
-  <si>
-    <t>0.6238,0.0334,0.5248,0.0008</t>
-  </si>
-  <si>
-    <t>0.6502,0.4801,0.0121,0.0003</t>
-  </si>
-  <si>
-    <t>0.3788,0.8318,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9898,0.0049,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.7772,0.2355,0.0368,0.0008</t>
-  </si>
-  <si>
-    <t>0.0114,0.4221,0.9605,0.0023</t>
-  </si>
-  <si>
-    <t>0.4393,0.3426,0.2985,0.0036</t>
-  </si>
-  <si>
-    <t>0.6288,0.3291,0.0638,0.0014</t>
-  </si>
-  <si>
-    <t>0.3237,0.7606,0.0238,0.0001</t>
-  </si>
-  <si>
-    <t>0.0412,0.9135,0.5184,0.0018</t>
-  </si>
-  <si>
-    <t>0.9515,0.0072,0.0304,0.0055</t>
-  </si>
-  <si>
-    <t>0.7558,0.0374,0.1399,0.0781</t>
-  </si>
-  <si>
-    <t>0.9858,0.0029,0.0058,0.0013</t>
-  </si>
-  <si>
-    <t>0.9020,0.0277,0.0180,0.0283</t>
-  </si>
-  <si>
-    <t>0.9497,0.0059,0.0460,0.0039</t>
-  </si>
-  <si>
-    <t>0.9673,0.0090,0.0033,0.0032</t>
-  </si>
-  <si>
-    <t>0.0864,0.8179,0.5333,0.0060</t>
-  </si>
-  <si>
-    <t>0.2260,0.2898,0.6806,0.0006</t>
-  </si>
-  <si>
-    <t>0.9698,0.0123,0.0132,0.0003</t>
-  </si>
-  <si>
-    <t>0.1363,0.5840,0.6349,0.0027</t>
-  </si>
-  <si>
-    <t>0.1070,0.6966,0.5071,0.0002</t>
-  </si>
-  <si>
-    <t>0.2727,0.6395,0.2135,0.0012</t>
-  </si>
-  <si>
-    <t>0.9706,0.0183,0.0033,0.0012</t>
-  </si>
-  <si>
-    <t>0.9433,0.0370,0.0054,0.0026</t>
-  </si>
-  <si>
-    <t>0.8347,0.1365,0.0169,0.0121</t>
-  </si>
-  <si>
-    <t>0.7512,0.2557,0.0174,0.0091</t>
-  </si>
-  <si>
-    <t>0.7679,0.1814,0.0084,0.0107</t>
-  </si>
-  <si>
-    <t>0.6500,0.2692,0.0116,0.0123</t>
-  </si>
-  <si>
-    <t>0.9101,0.0741,0.0142,0.0045</t>
-  </si>
-  <si>
-    <t>0.8023,0.0818,0.0094,0.0161</t>
-  </si>
-  <si>
-    <t>0.7882,0.1377,0.0124,0.0113</t>
-  </si>
-  <si>
-    <t>0.6173,0.3886,0.0153,0.0046</t>
-  </si>
-  <si>
-    <t>0.6926,0.1725,0.0106,0.0266</t>
-  </si>
-  <si>
-    <t>0.9384,0.0213,0.0083,0.0112</t>
-  </si>
-  <si>
-    <t>0.7373,0.0936,0.0092,0.0542</t>
-  </si>
-  <si>
-    <t>0.7171,0.2573,0.0092,0.0088</t>
-  </si>
-  <si>
-    <t>0.9480,0.0203,0.0063,0.0047</t>
-  </si>
-  <si>
-    <t>0.9157,0.0544,0.0049,0.0066</t>
-  </si>
-  <si>
-    <t>0.9038,0.0077,0.1724,0.0007</t>
-  </si>
-  <si>
-    <t>0.8757,0.0678,0.0515,0.0019</t>
-  </si>
-  <si>
-    <t>0.9886,0.0023,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.9692,0.0089,0.0174,0.0006</t>
-  </si>
-  <si>
-    <t>0.4852,0.5949,0.0032,0.0013</t>
-  </si>
-  <si>
-    <t>0.1762,0.8706,0.0036,0.0028</t>
-  </si>
-  <si>
-    <t>0.6611,0.4874,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.6807,0.4316,0.0055,0.0011</t>
-  </si>
-  <si>
-    <t>0.1817,0.8247,0.0082,0.0077</t>
-  </si>
-  <si>
-    <t>0.1744,0.8790,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.7236,0.4057,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.9903,0.0045,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9183,0.0240,0.0292,0.0043</t>
-  </si>
-  <si>
-    <t>0.9824,0.0046,0.0123,0.0002</t>
-  </si>
-  <si>
-    <t>0.9213,0.0431,0.0210,0.0043</t>
-  </si>
-  <si>
-    <t>0.6234,0.5232,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9753,0.0350,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.6958,0.3787,0.0076,0.0005</t>
-  </si>
-  <si>
-    <t>0.3769,0.5783,0.1201,0.0011</t>
-  </si>
-  <si>
-    <t>0.9589,0.0548,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.8155,0.3283,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9743,0.0436,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9821,0.0117,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.9231,0.0627,0.0057,0.0023</t>
-  </si>
-  <si>
-    <t>0.9708,0.0195,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.8574,0.1124,0.0215,0.0107</t>
-  </si>
-  <si>
-    <t>0.9192,0.0766,0.0086,0.0027</t>
-  </si>
-  <si>
-    <t>0.9715,0.0280,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.6967,0.2084,0.0449,0.0241</t>
-  </si>
-  <si>
-    <t>0.8538,0.1259,0.0131,0.0059</t>
-  </si>
-  <si>
-    <t>0.2541,0.6838,0.1408,0.0016</t>
-  </si>
-  <si>
-    <t>0.7883,0.1386,0.0848,0.0026</t>
-  </si>
-  <si>
-    <t>0.5137,0.3211,0.1745,0.0006</t>
-  </si>
-  <si>
-    <t>0.8778,0.0288,0.1288,0.0012</t>
-  </si>
-  <si>
-    <t>0.9733,0.0081,0.0154,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0012,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9656,0.0035,0.0578,0.0007</t>
-  </si>
-  <si>
-    <t>0.9586,0.0125,0.0165,0.0017</t>
-  </si>
-  <si>
-    <t>0.9725,0.0043,0.0203,0.0033</t>
-  </si>
-  <si>
-    <t>0.9348,0.0101,0.0305,0.0168</t>
-  </si>
-  <si>
-    <t>0.9813,0.0022,0.0074,0.0028</t>
-  </si>
-  <si>
-    <t>0.9864,0.0011,0.0074,0.0015</t>
-  </si>
-  <si>
-    <t>0.5829,0.2722,0.1753,0.0032</t>
-  </si>
-  <si>
-    <t>0.9675,0.0225,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.9436,0.0365,0.0244,0.0007</t>
-  </si>
-  <si>
-    <t>0.9023,0.0527,0.0093,0.0097</t>
-  </si>
-  <si>
-    <t>0.7658,0.2839,0.0032,0.0016</t>
-  </si>
-  <si>
-    <t>0.9516,0.0260,0.0067,0.0035</t>
-  </si>
-  <si>
-    <t>0.9643,0.0168,0.0059,0.0010</t>
-  </si>
-  <si>
-    <t>0.7451,0.1512,0.0359,0.0293</t>
-  </si>
-  <si>
-    <t>0.1200,0.5663,0.7321,0.0256</t>
-  </si>
-  <si>
-    <t>0.8131,0.1714,0.0104,0.0042</t>
-  </si>
-  <si>
-    <t>0.4366,0.4323,0.0160,0.0143</t>
-  </si>
-  <si>
-    <t>0.8977,0.0858,0.0096,0.0007</t>
-  </si>
-  <si>
-    <t>0.9849,0.0101,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0014,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7128,0.3293,0.0220,0.0014</t>
-  </si>
-  <si>
-    <t>0.9519,0.0280,0.0160,0.0008</t>
-  </si>
-  <si>
-    <t>0.9771,0.0247,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.8879,0.0755,0.0053,0.0030</t>
-  </si>
-  <si>
-    <t>0.9362,0.0385,0.0059,0.0042</t>
-  </si>
-  <si>
-    <t>0.8460,0.0676,0.0370,0.0209</t>
-  </si>
-  <si>
-    <t>0.9434,0.0173,0.0011,0.0041</t>
-  </si>
-  <si>
-    <t>0.8883,0.0661,0.0191,0.0121</t>
-  </si>
-  <si>
-    <t>0.9025,0.0842,0.0107,0.0039</t>
-  </si>
-  <si>
-    <t>0.8755,0.1107,0.0101,0.0042</t>
-  </si>
-  <si>
-    <t>0.8674,0.1146,0.0072,0.0056</t>
-  </si>
-  <si>
-    <t>0.9341,0.0712,0.0050,0.0008</t>
-  </si>
-  <si>
-    <t>0.9050,0.0771,0.0112,0.0032</t>
-  </si>
-  <si>
-    <t>0.3196,0.7033,0.0194,0.0038</t>
-  </si>
-  <si>
-    <t>0.8721,0.1015,0.0202,0.0030</t>
-  </si>
-  <si>
-    <t>0.7106,0.4002,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9566,0.0281,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.8419,0.0642,0.0047,0.0149</t>
-  </si>
-  <si>
-    <t>0.8826,0.1045,0.0120,0.0040</t>
-  </si>
-  <si>
-    <t>0.0449,0.4853,0.8129,0.0028</t>
-  </si>
-  <si>
-    <t>0.9737,0.0102,0.0100,0.0018</t>
-  </si>
-  <si>
-    <t>0.9330,0.0120,0.0731,0.0004</t>
-  </si>
-  <si>
-    <t>0.9594,0.0047,0.0567,0.0006</t>
-  </si>
-  <si>
-    <t>0.1412,0.6218,0.3929,0.0021</t>
-  </si>
-  <si>
-    <t>0.2867,0.4391,0.5193,0.0112</t>
-  </si>
-  <si>
-    <t>0.9701,0.0076,0.0257,0.0003</t>
-  </si>
-  <si>
-    <t>0.8835,0.0477,0.0477,0.0033</t>
-  </si>
-  <si>
-    <t>0.9452,0.0034,0.1269,0.0005</t>
-  </si>
-  <si>
-    <t>0.9777,0.0048,0.0135,0.0007</t>
-  </si>
-  <si>
-    <t>0.9861,0.0067,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.9724,0.0143,0.0072,0.0004</t>
-  </si>
-  <si>
-    <t>0.9843,0.0137,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9506,0.0498,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9803,0.0027,0.0163,0.0004</t>
-  </si>
-  <si>
-    <t>0.9914,0.0020,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9454,0.0190,0.0262,0.0010</t>
-  </si>
-  <si>
-    <t>0.9091,0.0799,0.0067,0.0028</t>
-  </si>
-  <si>
-    <t>0.8859,0.1309,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.7835,0.1830,0.0032,0.0022</t>
-  </si>
-  <si>
-    <t>0.8707,0.1251,0.0046,0.0024</t>
-  </si>
-  <si>
-    <t>0.9708,0.0342,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9664,0.0229,0.0061,0.0002</t>
-  </si>
-  <si>
-    <t>0.9945,0.0019,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9772,0.0016,0.0322,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0013,0.0139,0.0001</t>
-  </si>
-  <si>
-    <t>0.9700,0.0042,0.0319,0.0005</t>
-  </si>
-  <si>
-    <t>0.2891,0.0372,0.6786,0.0012</t>
-  </si>
-  <si>
-    <t>0.9179,0.0435,0.0299,0.0006</t>
-  </si>
-  <si>
-    <t>0.8016,0.0614,0.1512,0.0033</t>
-  </si>
-  <si>
-    <t>0.9298,0.0286,0.0286,0.0003</t>
-  </si>
-  <si>
-    <t>0.6457,0.0657,0.3825,0.0019</t>
-  </si>
-  <si>
-    <t>0.8378,0.0932,0.0050,0.0081</t>
-  </si>
-  <si>
-    <t>0.8059,0.1549,0.0154,0.0073</t>
-  </si>
-  <si>
-    <t>0.8722,0.1115,0.0036,0.0028</t>
-  </si>
-  <si>
-    <t>0.9189,0.0795,0.0128,0.0023</t>
-  </si>
-  <si>
-    <t>0.4808,0.4249,0.0165,0.0291</t>
-  </si>
-  <si>
-    <t>0.9086,0.0880,0.0044,0.0021</t>
-  </si>
-  <si>
-    <t>0.9401,0.0299,0.0033,0.0051</t>
-  </si>
-  <si>
-    <t>0.7814,0.2177,0.0047,0.0020</t>
-  </si>
-  <si>
-    <t>0.9381,0.0279,0.0341,0.0010</t>
-  </si>
-  <si>
-    <t>0.9409,0.0469,0.0042,0.0010</t>
-  </si>
-  <si>
-    <t>0.9530,0.0390,0.0061,0.0008</t>
-  </si>
-  <si>
-    <t>0.9842,0.0008,0.0377,0.0003</t>
-  </si>
-  <si>
-    <t>0.7434,0.0668,0.2381,0.0019</t>
-  </si>
-  <si>
-    <t>0.4342,0.1321,0.4707,0.0014</t>
-  </si>
-  <si>
-    <t>0.6761,0.0144,0.5471,0.0006</t>
-  </si>
-  <si>
-    <t>0.9321,0.0273,0.0273,0.0006</t>
-  </si>
-  <si>
-    <t>0.1111,0.0537,0.9452,0.0005</t>
-  </si>
-  <si>
-    <t>0.9149,0.0217,0.0708,0.0009</t>
-  </si>
-  <si>
-    <t>0.9921,0.0009,0.0097,0.0001</t>
-  </si>
-  <si>
-    <t>0.9826,0.0028,0.0150,0.0004</t>
-  </si>
-  <si>
-    <t>0.9937,0.0011,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9912,0.0014,0.0031,0.0004</t>
-  </si>
-  <si>
-    <t>0.9007,0.0750,0.0104,0.0050</t>
-  </si>
-  <si>
-    <t>0.5631,0.5027,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.9615,0.0156,0.0020,0.0043</t>
-  </si>
-  <si>
-    <t>0.9637,0.0362,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.8084,0.0339,0.0096,0.0552</t>
-  </si>
-  <si>
-    <t>0.8026,0.2010,0.0102,0.0028</t>
-  </si>
-  <si>
-    <t>0.9078,0.1053,0.0040,0.0007</t>
-  </si>
-  <si>
-    <t>0.7398,0.1657,0.0099,0.0229</t>
-  </si>
-  <si>
-    <t>0.9376,0.0158,0.0597,0.0011</t>
-  </si>
-  <si>
-    <t>0.6740,0.0402,0.3805,0.0006</t>
-  </si>
-  <si>
-    <t>0.8790,0.0226,0.1218,0.0006</t>
-  </si>
-  <si>
-    <t>0.9507,0.0106,0.0542,0.0008</t>
-  </si>
-  <si>
-    <t>0.9862,0.0017,0.0195,0.0001</t>
-  </si>
-  <si>
-    <t>0.9351,0.0250,0.0230,0.0022</t>
-  </si>
-  <si>
-    <t>0.9481,0.0301,0.0142,0.0004</t>
-  </si>
-  <si>
-    <t>0.9547,0.0060,0.0534,0.0032</t>
-  </si>
-  <si>
-    <t>0.9699,0.0120,0.0031,0.0018</t>
-  </si>
-  <si>
-    <t>0.9721,0.0036,0.0129,0.0044</t>
-  </si>
-  <si>
-    <t>0.9615,0.0074,0.0134,0.0068</t>
-  </si>
-  <si>
-    <t>0.9445,0.0042,0.0192,0.0217</t>
-  </si>
-  <si>
-    <t>0.9674,0.0041,0.0061,0.0085</t>
-  </si>
-  <si>
-    <t>0.9464,0.0260,0.0113,0.0040</t>
+    <t>0.8581,0.0655,0.0087,0.0574</t>
+  </si>
+  <si>
+    <t>0.0060,0.0011,0.0002,0.9972</t>
+  </si>
+  <si>
+    <t>0.4036,0.0044,0.0065,0.7173</t>
+  </si>
+  <si>
+    <t>0.0174,0.0016,0.0035,0.9888</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0016,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9975,0.0017,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0030,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9380,0.0002,0.2265,0.0001</t>
+  </si>
+  <si>
+    <t>0.4686,0.0060,0.7030,0.0006</t>
+  </si>
+  <si>
+    <t>0.7600,0.0081,0.3913,0.0012</t>
+  </si>
+  <si>
+    <t>0.0684,0.0143,0.9191,0.0019</t>
+  </si>
+  <si>
+    <t>0.9871,0.0029,0.0083,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.9958,0.0020,0.0026</t>
+  </si>
+  <si>
+    <t>0.0466,0.9601,0.0031,0.0023</t>
+  </si>
+  <si>
+    <t>0.1519,0.8857,0.0055,0.0018</t>
+  </si>
+  <si>
+    <t>0.0399,0.9750,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.0091,0.9889,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9555,0.0031,0.0390,0.0064</t>
+  </si>
+  <si>
+    <t>0.3784,0.0143,0.6525,0.0211</t>
+  </si>
+  <si>
+    <t>0.0104,0.0509,0.9612,0.0324</t>
+  </si>
+  <si>
+    <t>0.0559,0.0214,0.9191,0.0041</t>
+  </si>
+  <si>
+    <t>0.0290,0.0042,0.9705,0.0048</t>
+  </si>
+  <si>
+    <t>0.1707,0.0051,0.8324,0.0170</t>
+  </si>
+  <si>
+    <t>0.0014,0.0006,0.9962,0.0022</t>
+  </si>
+  <si>
+    <t>0.7351,0.4386,0.0042,0.0005</t>
+  </si>
+  <si>
+    <t>0.5356,0.3102,0.3062,0.0456</t>
+  </si>
+  <si>
+    <t>0.0015,0.0050,0.9935,0.0057</t>
+  </si>
+  <si>
+    <t>0.0157,0.9290,0.1255,0.0021</t>
+  </si>
+  <si>
+    <t>0.9092,0.0530,0.0350,0.0103</t>
+  </si>
+  <si>
+    <t>0.9299,0.0051,0.0729,0.0016</t>
+  </si>
+  <si>
+    <t>0.7406,0.4195,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.9955,0.0098,0.0001</t>
+  </si>
+  <si>
+    <t>0.0107,0.8930,0.0955,0.0188</t>
+  </si>
+  <si>
+    <t>0.0830,0.0199,0.8927,0.0318</t>
+  </si>
+  <si>
+    <t>0.0961,0.0056,0.9200,0.0025</t>
+  </si>
+  <si>
+    <t>0.6237,0.0095,0.2361,0.1120</t>
+  </si>
+  <si>
+    <t>0.0220,0.0759,0.9644,0.0015</t>
+  </si>
+  <si>
+    <t>0.0025,0.9924,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0141,0.0033,0.9804,0.0017</t>
+  </si>
+  <si>
+    <t>0.0769,0.8785,0.0278,0.1815</t>
+  </si>
+  <si>
+    <t>0.0011,0.9945,0.0036,0.0082</t>
+  </si>
+  <si>
+    <t>0.0042,0.9842,0.0156,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0230,0.0027,0.9814,0.0023</t>
+  </si>
+  <si>
+    <t>0.0057,0.0195,0.9888,0.0040</t>
+  </si>
+  <si>
+    <t>0.0129,0.0025,0.9595,0.0287</t>
+  </si>
+  <si>
+    <t>0.0544,0.0025,0.9601,0.0032</t>
+  </si>
+  <si>
+    <t>0.0037,0.1214,0.9912,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.0099,0.9902,0.0026</t>
+  </si>
+  <si>
+    <t>0.9398,0.1236,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9850,0.0031,0.0066,0.0033</t>
+  </si>
+  <si>
+    <t>0.9811,0.0194,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.0154,0.0598,0.9684,0.0136</t>
+  </si>
+  <si>
+    <t>0.9952,0.0059,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0017,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9693,0.0398,0.0068,0.0012</t>
+  </si>
+  <si>
+    <t>0.0042,0.8250,0.8927,0.0010</t>
+  </si>
+  <si>
+    <t>0.0279,0.2749,0.9655,0.0017</t>
+  </si>
+  <si>
+    <t>0.0180,0.0033,0.9826,0.0018</t>
+  </si>
+  <si>
+    <t>0.0028,0.9319,0.7258,0.0008</t>
+  </si>
+  <si>
+    <t>0.0029,0.0062,0.9876,0.0080</t>
+  </si>
+  <si>
+    <t>0.1431,0.8755,0.0182,0.0024</t>
+  </si>
+  <si>
+    <t>0.0314,0.9822,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9860,0.0106,0.0035,0.0022</t>
+  </si>
+  <si>
+    <t>0.9466,0.0127,0.0595,0.0041</t>
+  </si>
+  <si>
+    <t>0.0084,0.0368,0.9799,0.0037</t>
+  </si>
+  <si>
+    <t>0.0039,0.7818,0.8864,0.0013</t>
+  </si>
+  <si>
+    <t>0.0049,0.6189,0.8855,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.9864,0.0685,0.0021</t>
+  </si>
+  <si>
+    <t>0.0016,0.7206,0.9633,0.0009</t>
+  </si>
+  <si>
+    <t>0.0080,0.0002,0.0822,0.9611</t>
+  </si>
+  <si>
+    <t>0.0022,0.0014,0.0008,0.9981</t>
+  </si>
+  <si>
+    <t>0.0026,0.0003,0.0003,0.9988</t>
+  </si>
+  <si>
+    <t>0.1612,0.0015,0.0028,0.9340</t>
+  </si>
+  <si>
+    <t>0.0023,0.0059,0.0010,0.9968</t>
+  </si>
+  <si>
+    <t>0.0060,0.0254,0.0042,0.9912</t>
+  </si>
+  <si>
+    <t>0.0006,0.9402,0.9294,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.4025,0.9830,0.0002</t>
+  </si>
+  <si>
+    <t>0.1425,0.1643,0.7016,0.0348</t>
+  </si>
+  <si>
+    <t>0.0010,0.8982,0.9729,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.9171,0.9714,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.7486,0.8381,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0016,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9929,0.0053,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9873,0.0137,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.9877,0.0033,0.0011,0.0050</t>
+  </si>
+  <si>
+    <t>0.9965,0.0037,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9955,0.0038,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9875,0.0142,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0027,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9951,0.0018,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0211,0.0076,0.9851,0.0014</t>
+  </si>
+  <si>
+    <t>0.0728,0.0189,0.9391,0.0008</t>
+  </si>
+  <si>
+    <t>0.8208,0.0381,0.1274,0.0211</t>
+  </si>
+  <si>
+    <t>0.0026,0.0021,0.9936,0.0010</t>
+  </si>
+  <si>
+    <t>0.7101,0.4657,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.0484,0.9701,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.1093,0.9340,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.0397,0.9664,0.0013,0.0064</t>
+  </si>
+  <si>
+    <t>0.0372,0.9761,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.0311,0.9800,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.3560,0.7734,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.6803,0.0613,0.2437,0.0069</t>
+  </si>
+  <si>
+    <t>0.3452,0.0368,0.6357,0.0418</t>
+  </si>
+  <si>
+    <t>0.5450,0.1285,0.3561,0.0367</t>
+  </si>
+  <si>
+    <t>0.9464,0.0042,0.0483,0.0024</t>
+  </si>
+  <si>
+    <t>0.1125,0.0683,0.8578,0.0175</t>
+  </si>
+  <si>
+    <t>0.0198,0.9696,0.0115,0.0015</t>
+  </si>
+  <si>
+    <t>0.0031,0.9895,0.0047,0.0014</t>
+  </si>
+  <si>
+    <t>0.0245,0.9596,0.0138,0.0426</t>
+  </si>
+  <si>
+    <t>0.0007,0.9312,0.9070,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9973,0.0111,0.0000</t>
+  </si>
+  <si>
+    <t>0.5324,0.5147,0.0339,0.0013</t>
+  </si>
+  <si>
+    <t>0.8849,0.2310,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0019,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0008,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9921,0.0029,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9951,0.0025,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0010,0.0012,0.0043</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0026,0.3220,0.8875,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.1451,0.9834,0.0010</t>
+  </si>
+  <si>
+    <t>0.0173,0.0485,0.9397,0.0022</t>
+  </si>
+  <si>
+    <t>0.0154,0.0751,0.9673,0.0005</t>
+  </si>
+  <si>
+    <t>0.9016,0.0540,0.0158,0.0269</t>
+  </si>
+  <si>
+    <t>0.7372,0.0032,0.4058,0.0017</t>
+  </si>
+  <si>
+    <t>0.8206,0.0013,0.3531,0.0032</t>
+  </si>
+  <si>
+    <t>0.5273,0.0877,0.4808,0.0310</t>
+  </si>
+  <si>
+    <t>0.0340,0.0006,0.0023,0.9848</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0030,0.0017,0.0039,0.9962</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.0030,0.9987</t>
+  </si>
+  <si>
+    <t>0.0054,0.8352,0.4212,0.0044</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.6609,0.4506,0.0048,0.0058</t>
+  </si>
+  <si>
+    <t>0.9959,0.0023,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.1373,0.9277,0.0030,0.0010</t>
+  </si>
+  <si>
+    <t>0.9808,0.0068,0.0032,0.0052</t>
+  </si>
+  <si>
+    <t>0.1090,0.0134,0.0080,0.9327</t>
+  </si>
+  <si>
+    <t>0.9872,0.0042,0.0038,0.0033</t>
+  </si>
+  <si>
+    <t>0.0125,0.0075,0.9755,0.0149</t>
+  </si>
+  <si>
+    <t>0.5172,0.0002,0.0011,0.6824</t>
+  </si>
+  <si>
+    <t>0.6937,0.0258,0.0158,0.2796</t>
+  </si>
+  <si>
+    <t>0.8913,0.1006,0.0196,0.0090</t>
+  </si>
+  <si>
+    <t>0.9578,0.0254,0.0071,0.0074</t>
+  </si>
+  <si>
+    <t>0.9939,0.0026,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.5278,0.3703,0.1078,0.0181</t>
+  </si>
+  <si>
+    <t>0.2179,0.4135,0.4354,0.0102</t>
+  </si>
+  <si>
+    <t>0.9662,0.0289,0.0034,0.0039</t>
+  </si>
+  <si>
+    <t>0.9903,0.0041,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0027,0.0016</t>
+  </si>
+  <si>
+    <t>0.9898,0.0036,0.0027,0.0021</t>
+  </si>
+  <si>
+    <t>0.9947,0.0012,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9226,0.1605,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.3177,0.7528,0.0258,0.0019</t>
+  </si>
+  <si>
+    <t>0.8173,0.3055,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9662,0.0210,0.0118,0.0093</t>
+  </si>
+  <si>
+    <t>0.9955,0.0029,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9768,0.0263,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9921,0.0053,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9679,0.0440,0.0021,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.0515,0.9946,0.0013</t>
+  </si>
+  <si>
+    <t>0.9595,0.0337,0.0096,0.0023</t>
+  </si>
+  <si>
+    <t>0.0028,0.0055,0.9924,0.0009</t>
+  </si>
+  <si>
+    <t>0.0560,0.1513,0.8902,0.0197</t>
+  </si>
+  <si>
+    <t>0.0642,0.0033,0.9517,0.0013</t>
+  </si>
+  <si>
+    <t>0.0082,0.0431,0.9863,0.0028</t>
+  </si>
+  <si>
+    <t>0.0026,0.0457,0.9895,0.0033</t>
+  </si>
+  <si>
+    <t>0.0050,0.0045,0.9852,0.0039</t>
+  </si>
+  <si>
+    <t>0.0330,0.0097,0.9709,0.0019</t>
+  </si>
+  <si>
+    <t>0.1486,0.0081,0.9099,0.0005</t>
+  </si>
+  <si>
+    <t>0.1055,0.0632,0.7621,0.0667</t>
+  </si>
+  <si>
+    <t>0.5470,0.0277,0.5074,0.0076</t>
+  </si>
+  <si>
+    <t>0.0670,0.0721,0.8888,0.0010</t>
+  </si>
+  <si>
+    <t>0.0692,0.3198,0.4910,0.0007</t>
+  </si>
+  <si>
+    <t>0.3324,0.0997,0.5424,0.0189</t>
+  </si>
+  <si>
+    <t>0.8408,0.0097,0.2067,0.0091</t>
+  </si>
+  <si>
+    <t>0.0940,0.0275,0.8448,0.0343</t>
+  </si>
+  <si>
+    <t>0.8939,0.1925,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.9528,0.0935,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9965,0.0031,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9749,0.0472,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.8804,0.1667,0.0208,0.0071</t>
+  </si>
+  <si>
+    <t>0.8976,0.0159,0.0750,0.0045</t>
+  </si>
+  <si>
+    <t>0.8910,0.0034,0.1535,0.0052</t>
+  </si>
+  <si>
+    <t>0.4642,0.0047,0.0410,0.5291</t>
+  </si>
+  <si>
+    <t>0.4668,0.0047,0.6883,0.0044</t>
+  </si>
+  <si>
+    <t>0.8214,0.0049,0.2072,0.0081</t>
+  </si>
+  <si>
+    <t>0.0022,0.0008,0.9925,0.0032</t>
+  </si>
+  <si>
+    <t>0.0454,0.2991,0.8625,0.0148</t>
+  </si>
+  <si>
+    <t>0.0206,0.2210,0.9406,0.0221</t>
+  </si>
+  <si>
+    <t>0.3680,0.0009,0.8096,0.0013</t>
+  </si>
+  <si>
+    <t>0.0147,0.0495,0.9463,0.0037</t>
+  </si>
+  <si>
+    <t>0.9780,0.0071,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9943,0.0034,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9918,0.0039,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9933,0.0074,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9898,0.0097,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9960,0.0028,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0027,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9967,0.0014,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.1159,0.0080,0.9337,0.0014</t>
+  </si>
+  <si>
+    <t>0.1093,0.0765,0.8295,0.0175</t>
+  </si>
+  <si>
+    <t>0.9884,0.0040,0.0048,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9984,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0551,0.9812,0.0055</t>
+  </si>
+  <si>
+    <t>0.0025,0.2352,0.9729,0.0038</t>
+  </si>
+  <si>
+    <t>0.0080,0.0018,0.9940,0.0003</t>
+  </si>
+  <si>
+    <t>0.0613,0.0163,0.9363,0.0044</t>
+  </si>
+  <si>
+    <t>0.0014,0.0096,0.9969,0.0010</t>
+  </si>
+  <si>
+    <t>0.0142,0.0427,0.9569,0.0078</t>
+  </si>
+  <si>
+    <t>0.5838,0.0254,0.4770,0.0025</t>
+  </si>
+  <si>
+    <t>0.9762,0.0016,0.0361,0.0007</t>
+  </si>
+  <si>
+    <t>0.9413,0.0004,0.1516,0.0008</t>
+  </si>
+  <si>
+    <t>0.9471,0.0030,0.0646,0.0050</t>
+  </si>
+  <si>
+    <t>0.9958,0.0017,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9938,0.0027,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9961,0.0023,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0019,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9902,0.0113,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0630,0.0618,0.8629,0.0100</t>
+  </si>
+  <si>
+    <t>0.0138,0.1006,0.9551,0.0020</t>
+  </si>
+  <si>
+    <t>0.0105,0.0132,0.9705,0.0047</t>
+  </si>
+  <si>
+    <t>0.0486,0.0125,0.9278,0.0017</t>
+  </si>
+  <si>
+    <t>0.0562,0.0011,0.9753,0.0007</t>
+  </si>
+  <si>
+    <t>0.2317,0.0454,0.3430,0.5041</t>
+  </si>
+  <si>
+    <t>0.0452,0.0412,0.9359,0.0107</t>
+  </si>
+  <si>
+    <t>0.0265,0.0211,0.9458,0.0120</t>
+  </si>
+  <si>
+    <t>0.9585,0.0006,0.0022,0.0392</t>
+  </si>
+  <si>
+    <t>0.3435,0.0045,0.0022,0.8080</t>
+  </si>
+  <si>
+    <t>0.0947,0.0067,0.0061,0.9534</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.0017,0.9991</t>
+  </si>
+  <si>
+    <t>0.0046,0.0001,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.7333,0.0222,0.2718,0.0650</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
         <v>467</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5229,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D236" t="s">
         <v>498</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
